--- a/evaluation_forms/014_focus_group_screener_form--evaluation_forms.xlsx
+++ b/evaluation_forms/014_focus_group_screener_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'employed_part-time'}</t>
+          <t>employed_part-time</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Employed part-time'}</t>
+          <t>Employed part-time</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'self_employed'}</t>
+          <t>self_employed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Self Employed'}</t>
+          <t>Self Employed</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_20,000'}</t>
+          <t>less_than_20,000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 20,000'}</t>
+          <t>Less than 20,000</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'20,000_to_40,000'}</t>
+          <t>20,000_to_40,000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '20,000 to 40,000'}</t>
+          <t>20,000 to 40,000</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'40,000_to_60,000'}</t>
+          <t>40,000_to_60,000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '40,000 to 60,000'}</t>
+          <t>40,000 to 60,000</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'60,000_to_80,000'}</t>
+          <t>60,000_to_80,000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '60,000 to 80,000'}</t>
+          <t>60,000 to 80,000</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'80,000_or_more'}</t>
+          <t>80,000_or_more</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '80,000 or more'}</t>
+          <t>80,000 or more</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'high_school_diploma'}</t>
+          <t>high_school_diploma</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'High school diploma'}</t>
+          <t>High school diploma</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Some college'}</t>
+          <t>Some college</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_"bachelor's_degree"}</t>
+          <t>bachelor's_degree</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': "Bachelor's degree"}</t>
+          <t>Bachelor's degree</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'advanced_degree'}</t>
+          <t>advanced_degree</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Advanced degree'}</t>
+          <t>Advanced degree</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Chinese'}</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'caucasian'}</t>
+          <t>caucasian</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Caucasian'}</t>
+          <t>Caucasian</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'african_american'}</t>
+          <t>african_american</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'African American'}</t>
+          <t>African American</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'asian'}</t>
+          <t>asian</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Asian'}</t>
+          <t>Asian</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'latin_american'}</t>
+          <t>latin_american</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Latin American'}</t>
+          <t>Latin American</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'married'}</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Married'}</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'divorced'}</t>
+          <t>divorced</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Divorced'}</t>
+          <t>Divorced</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'widowed'}</t>
+          <t>widowed</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Widowed'}</t>
+          <t>Widowed</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_12th_grade'}</t>
+          <t>less_than_12th_grade</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 12th grade'}</t>
+          <t>Less than 12th grade</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'12th_grade'}</t>
+          <t>12th_grade</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': '12th grade'}</t>
+          <t>12th grade</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_"bachelor's_degree"}</t>
+          <t>bachelor's_degree</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': "Bachelor's degree"}</t>
+          <t>Bachelor's degree</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'advanced_degree'}</t>
+          <t>advanced_degree</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Advanced degree'}</t>
+          <t>Advanced degree</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'high_school_diploma'}</t>
+          <t>high_school_diploma</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'High school diploma'}</t>
+          <t>High school diploma</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Some college'}</t>
+          <t>Some college</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_"bachelor's_degree"}</t>
+          <t>bachelor's_degree</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': "Bachelor's degree"}</t>
+          <t>Bachelor's degree</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'advanced_degree'}</t>
+          <t>advanced_degree</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Advanced degree'}</t>
+          <t>Advanced degree</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'high_school_diploma'}</t>
+          <t>high_school_diploma</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'High school diploma'}</t>
+          <t>High school diploma</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Some college'}</t>
+          <t>Some college</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_"bachelor's_degree"}</t>
+          <t>bachelor's_degree</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': "Bachelor's degree"}</t>
+          <t>Bachelor's degree</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'advanced_degree'}</t>
+          <t>advanced_degree</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Advanced degree'}</t>
+          <t>Advanced degree</t>
         </is>
       </c>
     </row>
